--- a/data/si2_c14_sites.xlsx
+++ b/data/si2_c14_sites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\资料\学科\考古学\02新石器\华南\农业-狩猎采集互动 华南 模型\2026 文章\ABM-South China - 26.8.16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\资料\学科\考古学\02新石器\华南\农业-狩猎采集互动 华南 模型\2026 文章\ABM-South China - 26.8.31\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C372F7-BA16-40BC-B992-12346BBEAFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA9F145-312A-46DD-81F9-71C17183006B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4133" yWindow="2618" windowWidth="14422" windowHeight="7155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sites" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="429">
   <si>
     <t>Baitoushan</t>
   </si>
@@ -3448,6 +3448,47 @@
   </si>
   <si>
     <t>farming</t>
+  </si>
+  <si>
+    <t>Zhuangbianshan</t>
+  </si>
+  <si>
+    <t>庄边山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Beta-347604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ma T et al., 2016 Veget Hist Archaeobot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New evidence for Neolithic rice cultivation and Holocene environmental change in the Fuzhou Basin, southeast China</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.1007/s00334-016-0556-0</t>
+  </si>
+  <si>
+    <t>Settlement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Systematic excavation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3600,7 +3641,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3647,6 +3688,9 @@
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9553,29 +9597,75 @@
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="5"/>
-      <c r="V80" s="10"/>
-      <c r="W80" s="10"/>
+      <c r="A80" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H80" s="8">
+        <v>119.14100000000001</v>
+      </c>
+      <c r="I80" s="8">
+        <v>26.103000000000002</v>
+      </c>
+      <c r="J80" s="7">
+        <v>25</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="O80" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="P80" s="7">
+        <v>4350</v>
+      </c>
+      <c r="Q80" s="7">
+        <v>30</v>
+      </c>
+      <c r="R80" s="7">
+        <v>4500</v>
+      </c>
+      <c r="S80" s="7">
+        <v>4230</v>
+      </c>
+      <c r="T80" s="7">
+        <v>2016</v>
+      </c>
+      <c r="U80" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="V80" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="W80" s="5" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A81" s="7"/>
@@ -13460,7 +13550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5601487D-9C83-48B8-8EAC-2CB1DAFE1179}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.86328125" style="11" customWidth="1"/>
@@ -13935,133 +14025,148 @@
         <v>231</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2016</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B33" s="9">
         <v>1996</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D33" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E33" s="15" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="13" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B34" s="13">
         <v>1990</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E34" s="14" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="B34" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B35" s="9">
+        <v>2016</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B36" s="9">
         <v>2018</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E36" s="15" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="13" t="s">
+    <row r="37" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B37" s="13">
         <v>1985</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13" t="s">
+      <c r="C37" s="13"/>
+      <c r="D37" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E37" s="14" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B37" s="9">
-        <v>2017</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E37" s="15"/>
     </row>
     <row r="38" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="B38" s="9">
-        <v>1987</v>
+        <v>2017</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>330</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="E38" s="15"/>
     </row>
     <row r="39" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="9">
+        <v>1987</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B40" s="9">
         <v>1994</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D40" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E40" s="15" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A40" s="13" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B41" s="13">
         <v>2005</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13" t="s">
+      <c r="C41" s="13"/>
+      <c r="D41" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E41" s="14" t="s">
         <v>257</v>
       </c>
     </row>
